--- a/daily_matches/job_matches_2026-03-23.xlsx
+++ b/daily_matches/job_matches_2026-03-23.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LLM/Machine Learning Engineering Summer Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, TensorFlow, PyTorch</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b2394c0f0453e3</t>
+          <t>https://www.indeed.com/viewjob?jk=20c3803f586deedc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Software Engineer - Site Reliability</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FriendliAI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, RAG, Hugging Face, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=715b1105e40c51bd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI / Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DNV KEMA Energy &amp; Sustainability</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Git, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff8045f64f24fe43</t>
+          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer - Machine Learning</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>Generative AI, RAG, PyTorch, AWS SageMaker, Git, Hadoop, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e558de94bb1969ce</t>
+          <t>https://www.indeed.com/viewjob?jk=e4fa376cb1aac719</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Software Engineer – AI Agents</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>FriendliAI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hadoop, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Kubernetes, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9709ec31f7fa2177</t>
+          <t>https://www.indeed.com/viewjob?jk=af74cd40e9546338</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-23.xlsx
+++ b/daily_matches/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,157 +468,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Agentic Solutions Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, Git, Databricks</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c3803f586deedc</t>
+          <t>https://www.indeed.com/viewjob?jk=799a4939da5328d7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer - Site Reliability</t>
+          <t>Machine Learning Engineer – Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FriendliAI</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715b1105e40c51bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a88d70cbd872dd34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Energy</t>
+          <t>Machine Learning Engineer – Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DNV KEMA Energy &amp; Sustainability</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea8d61e353dcf3fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8c9ca843965aa885</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - Machine Learning</t>
+          <t>Machine Learning Engineer – Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, PyTorch, AWS SageMaker, Git, Hadoop, Python, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4fa376cb1aac719</t>
+          <t>https://www.indeed.com/viewjob?jk=7da558975bfac95d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer – AI Agents</t>
+          <t>Machine Learning Engineer – Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FriendliAI</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,507 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Kubernetes, Python, R, Scala</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af74cd40e9546338</t>
+          <t>https://www.indeed.com/viewjob?jk=874ed609e05a7bfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f38959bb559bfb98</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6338c73031405538</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36f1c9cdcacb3136</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b5a3910353244c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43414fba14d62247</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37cba859ef4d9fb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dde68f50f77e5e76</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08efe7ae7ed57a90</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84e8b903de8f9821</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a35e56d4b4e14ca9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d5a13f7284fe6af</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=946598a19a640df8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5de16df324629d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Remote</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>YO IT CONSULTING</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c00245e5543348a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-23.xlsx
+++ b/daily_matches/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agentic Solutions Developer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>Bentley Systems</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, Python</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799a4939da5328d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8766b681045861f3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88d70cbd872dd34</t>
+          <t>https://www.indeed.com/viewjob?jk=8a7be29572b27f0f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, Apache Airflow, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c9ca843965aa885</t>
+          <t>https://www.indeed.com/viewjob?jk=47eccd8521d84b42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7da558975bfac95d</t>
+          <t>https://www.indeed.com/viewjob?jk=568d6169d76666f1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874ed609e05a7bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b05b3b46caa4257a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38959bb559bfb98</t>
+          <t>https://www.indeed.com/viewjob?jk=79fac182fa25939d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Helena, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6338c73031405538</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5d55da591824b1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36f1c9cdcacb3136</t>
+          <t>https://www.indeed.com/viewjob?jk=b65be6be8460bd78</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5a3910353244c4</t>
+          <t>https://www.indeed.com/viewjob?jk=17e6aac4359b9fd3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43414fba14d62247</t>
+          <t>https://www.indeed.com/viewjob?jk=c59949bd00d83e90</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37cba859ef4d9fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8ef170ca8fbcbe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde68f50f77e5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=373d8c47a07bc6b1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08efe7ae7ed57a90</t>
+          <t>https://www.indeed.com/viewjob?jk=a84b0a6dbbfaaa46</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84e8b903de8f9821</t>
+          <t>https://www.indeed.com/viewjob?jk=f8368adff4982153</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35e56d4b4e14ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=66f77cbc8591aaa1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Medford, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5a13f7284fe6af</t>
+          <t>https://www.indeed.com/viewjob?jk=bb419979ad314a75</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Troy, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=946598a19a640df8</t>
+          <t>https://www.indeed.com/viewjob?jk=9322c1d0c3fbb74d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,42 +1091,497 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5de16df324629d7</t>
+          <t>https://www.indeed.com/viewjob?jk=079310cd3af87092</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer – Remote</t>
+          <t>Senior Machine Learning Engineer - Energy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>DNV</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40c0504d51145ec2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=307370dbe3caf012</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=becb707558951aa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4aff12f1bcf2fce</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e88e9dd515938e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f9314a3f9b0e1d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d66efbee602a7577</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Middletown, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de57038afd5f7ffa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4173afb3af02e847</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc0e5eb74e1013b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Energy</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8be0210ffb983e8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI/ML Intern</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Parahunt Global Solutions</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Gruver, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2376b6c4753bdf2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Fircosoft Software Engineer – Fircosoft- Columbus, OH</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RSHARMA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>10</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c00245e5543348a</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, Kafka, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0fbbbc0264c2998</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IT, Cloud &amp; AI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>United States Steel</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Osceola, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Hugging Face, TensorFlow, PyTorch, S3, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd84f3aefec029b0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-23.xlsx
+++ b/daily_matches/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A.I. Developer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mindset Care, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Kubernetes, CI/CD</t>
+          <t>RAG, Azure ML, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19124af0add103c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed0702643990e72</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist Microsoft Fabric &amp; Azure Synapse (100% Remoto)</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SMX USA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>West Lake, LA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>27.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, Synapse, CI/CD, Git, PySpark, Power BI, Python, SQL, R</t>
+          <t>RAG, Azure ML, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a1c428568431f9</t>
+          <t>https://www.indeed.com/viewjob?jk=51d2af5d54195fff</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Python, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ced8db3399560bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cloud Resources</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FastAPI, Docker, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,497 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9752e4f115e95051</t>
+          <t>https://www.indeed.com/viewjob?jk=d75f82bc9353e156</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer – Enterprise Generative AI Platform UI and Python Engineering</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=424e8ed57c8af088</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d58d41b60fc01d72</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Netwrix</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Azure ML, Kubernetes, CI/CD, Terraform, Git, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Python Developer-2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41debd8fcf354c63</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python Developer-2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60549b188cc8a31b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Python Developer-2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd18a211ab22374b</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, FAISS, Pinecone, TensorFlow, PyTorch, Docker, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b94ce61ad979a01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>API Security Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc10b8f854da7e30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Upstart</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Matplotlib, Python, SQL, R, Scala, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82b9fde7b04bb162</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31e64e2fc1b30704</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97ad725c238fe9f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Scientist-4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe28579aea4d7255</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, PySpark, Kafka, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebaefb91ade88a60</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Implementation Specialist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hitachi Digital Services</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22e1c684dc944566</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lennar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, S3, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-23.xlsx
+++ b/daily_matches/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Senior AI/ML Engineer - MLOps &amp; Production AI Systems - Remote or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
+          <t>Generative AI, TensorFlow, PyTorch, Azure ML, Kinesis, MLflow, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed0702643990e72</t>
+          <t>https://www.indeed.com/viewjob?jk=8efb3901b9a2f678</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>West Lake, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
+          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, Databricks, PostgreSQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d2af5d54195fff</t>
+          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Snowflake</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b13e7f95cc76df1</t>
+          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Engineer III - Frontend (Global Dining)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75f82bc9353e156</t>
+          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Senior Software Engineer, Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Learning Commons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424e8ed57c8af088</t>
+          <t>https://www.indeed.com/viewjob?jk=c25e193ad033c62e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>DevOps Engineer - Ai - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>YO IT CONSULTING</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d58d41b60fc01d72</t>
+          <t>https://www.indeed.com/viewjob?jk=90769268b589029f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Associate - AWS Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Netwrix</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Azure ML, Kubernetes, CI/CD, Terraform, Git, Databricks, Python</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eb3e0fbf0cc806</t>
+          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Developer-2</t>
+          <t>Azure Site Reliability &amp; Automation Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Innovative Systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41debd8fcf354c63</t>
+          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Developer-2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>DomainTools</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>RAG, Docker, Kubernetes, Apache Airflow, Kafka, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60549b188cc8a31b</t>
+          <t>https://www.indeed.com/viewjob?jk=af786696ca3d5562</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Python Developer-2</t>
+          <t>AI / Computer Science Intern (Automation &amp; Data Systems)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Apsis Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>RAG, TensorFlow, PyTorch, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd18a211ab22374b</t>
+          <t>https://www.indeed.com/viewjob?jk=48182d5d9b36c996</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, FAISS, Pinecone, TensorFlow, PyTorch, Docker, CI/CD, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b94ce61ad979a01</t>
+          <t>https://www.indeed.com/viewjob?jk=e14a2c939b76bd2f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Sales Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Britive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python</t>
+          <t>S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc10b8f854da7e30</t>
+          <t>https://www.indeed.com/viewjob?jk=37aecd6fd13375e7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior GenAI Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Matplotlib, Python, SQL, R, Scala, Hypothesis Testing, A/B Testing</t>
+          <t>Data Scientist, RAG, Copilot, FastAPI, CI/CD, Databricks, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b9fde7b04bb162</t>
+          <t>https://www.indeed.com/viewjob?jk=6efa4c4468b044dc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e64e2fc1b30704</t>
+          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, R, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ad725c238fe9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist-4</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>T. Mims Corp.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, PySpark, Kafka, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>Prompt Engineering, TensorFlow, PyTorch, Git, PySpark, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebaefb91ade88a60</t>
+          <t>https://www.indeed.com/viewjob?jk=1e676bd6e85d27d5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Implementation Specialist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>Richtech Creative Displays</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e1c684dc944566</t>
+          <t>https://www.indeed.com/viewjob?jk=d5b649e96f7e4c0b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Business Systems Analyst – Voice of Customer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Genesys</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,217 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3ac54f02015073</t>
+          <t>https://www.indeed.com/viewjob?jk=5f0ac0d262537749</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Junior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Coalfire</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Skechers</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rancho Belago, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=740eb524a37ebb9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Skechers</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Manhattan Beach, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d862aca06fdf52c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Global Veterinary Pharmacovigilance, Signal Management</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52e3567edae6c808</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Marketing Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Arthrex</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=049ff583d84689dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Analytics</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Discord</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66247a3138fa9481</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-23.xlsx
+++ b/daily_matches/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer - MLOps &amp; Production AI Systems - Remote or Hybrid in MN/DC</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>T. Mims Corp.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, Azure ML, Kinesis, MLflow, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, MLflow, FastAPI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8efb3901b9a2f678</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c88bf4c3538dd3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, Databricks, PostgreSQL, NoSQL, Python</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7caafc9fc9ff0d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e531a99f92881416</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud DevOps Engineer</t>
+          <t>Senior Specialist - Data Sciences</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Mistral, Pinecone, ChromaDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8158e5b52e0208bc</t>
+          <t>https://www.indeed.com/viewjob?jk=acc07ca5d56ddef2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend (Global Dining)</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MySQL, MongoDB, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22085e4edc6fdc63</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c845d7e501ec86</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform</t>
+          <t>Data Engineer (Cloud Data Platforms)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Learning Commons</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, R</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25e193ad033c62e</t>
+          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Ai - Remote</t>
+          <t>Technical Data Engineer - Level II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YO IT CONSULTING</t>
+          <t>S &amp; K Technologies, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warner Robins, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Apache Airflow, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90769268b589029f</t>
+          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Associate - AWS Engineer</t>
+          <t>Senior Production Engineer - hybrid in Santa Clara, CA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>CyberArk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66effda273eb3723</t>
+          <t>https://www.indeed.com/viewjob?jk=e0363daba82d95c7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Site Reliability &amp; Automation Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Innovative Systems</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abfdcefe625a5d98</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ce6a4d55d2ceb1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Materials Scientist - AI/ML for Materials Design</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DomainTools</t>
+          <t>Avery Dennison</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Apache Airflow, Kafka, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af786696ca3d5562</t>
+          <t>https://www.indeed.com/viewjob?jk=27d073c89cda0684</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI / Computer Science Intern (Automation &amp; Data Systems)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Apsis Solutions</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Databricks, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48182d5d9b36c996</t>
+          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Databricks, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e14a2c939b76bd2f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sales Engineer</t>
+          <t>AI DevOps Engineering Intern</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Britive</t>
+          <t>Nabors Industries</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37aecd6fd13375e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f92799868c5370</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior GenAI Platform Engineer</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, FastAPI, CI/CD, Databricks, SQL, R, Scala</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efa4c4468b044dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8d16cacc55a79a65</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3a6f36401116ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e03ea52757f6c20a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b55dc8877ac2f74</t>
+          <t>https://www.indeed.com/viewjob?jk=130823613412f45e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Intern</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T. Mims Corp.</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Prompt Engineering, TensorFlow, PyTorch, Git, PySpark, Python, R, Scala, Optimization</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e676bd6e85d27d5</t>
+          <t>https://www.indeed.com/viewjob?jk=49aad56d323b86fc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Richtech Creative Displays</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Python, R, Scala</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5b649e96f7e4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=b692d4b4514efb8e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst – Voice of Customer</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Genesys</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, SQL, R</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f0ac0d262537749</t>
+          <t>https://www.indeed.com/viewjob?jk=aadf94f6c3802590</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Junior Site Reliability Engineer</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Coalfire</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849f18264b0353d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0d820b6fb355e099</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Salesforce Engineer</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rancho Belago, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740eb524a37ebb9b</t>
+          <t>https://www.indeed.com/viewjob?jk=260d2c211e08604c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Salesforce Engineer</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d862aca06fdf52c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ad6c3c6ab5aadbf7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Global Veterinary Pharmacovigilance, Signal Management</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e3567edae6c808</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb44cf89ffe8d69</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marketing Data Scientist I</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arthrex</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049ff583d84689dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e2eed596f2550187</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Analytics</t>
+          <t>Senior Frontend Engineer, Growth</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, SQL, R, Scala, A/B Testing</t>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,287 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66247a3138fa9481</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba069fa2aa10643</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Frontend Engineer, Growth</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c410cf2e6ed6cf30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Frontend Engineer, Growth</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dae6cea31770b11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Frontend Engineer, Growth</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a690d8865abae1e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Frontend Engineer, Growth</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62ec4d7e57257fa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Frontend Engineer, Growth</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb5fcb7e9a3cd5fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Frontend Engineer, Growth</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37cbf38f16601053</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Frontend Engineer, Growth</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Scribd, Inc.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f2c978f71265748</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Entry Level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>S3, Git, PostgreSQL, MongoDB, Dask, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-23.xlsx
+++ b/daily_matches/job_matches_2026-03-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior GenAI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T. Mims Corp.</t>
+          <t>National Basketball Association</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, MLflow, FastAPI, CI/CD, Git</t>
+          <t>AI Engineer, Generative AI, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Git, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c88bf4c3538dd3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8ba25f9a038e12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e531a99f92881416</t>
+          <t>https://www.indeed.com/viewjob?jk=c14d8d29c2cadb59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Specialist - Data Sciences</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Mistral, Pinecone, ChromaDB, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, S3, Kinesis, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acc07ca5d56ddef2</t>
+          <t>https://www.indeed.com/viewjob?jk=8891e7776cfef98e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Senior Software Engineer - Onsite Interviews (Denver)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Jenkins, Terraform, R, Java</t>
+          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c845d7e501ec86</t>
+          <t>https://www.indeed.com/viewjob?jk=cb173fd010bc37d5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (Cloud Data Platforms)</t>
+          <t>Specialist Software Engineering - Onsite Interviews (Denver)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, Kafka, Python, SQL</t>
+          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63baf65c571965b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec5847773fc77b8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technical Data Engineer - Level II</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S &amp; K Technologies, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Warner Robins, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Apache Airflow, Kafka, Hadoop, Python, SQL, R</t>
+          <t>RAG, S3, MLflow, Kubernetes, Apache Airflow, Terraform, Git, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de7a704f3453571d</t>
+          <t>https://www.indeed.com/viewjob?jk=4da96d1220654c8a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Production Engineer - hybrid in Santa Clara, CA</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CyberArk</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, CI/CD, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0363daba82d95c7</t>
+          <t>https://www.indeed.com/viewjob?jk=d3e4f860abba1b64</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
+          <t>RAG, CI/CD, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ce6a4d55d2ceb1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f32c0a302cd469c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Materials Scientist - AI/ML for Materials Design</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Avery Dennison</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mentor, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization, Bayesian</t>
+          <t>RAG, CI/CD, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27d073c89cda0684</t>
+          <t>https://www.indeed.com/viewjob?jk=ec49aaf6d851f31a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Data Innovation and Tools Rationalization</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Databricks, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, CI/CD, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c023eaaf370dc19c</t>
+          <t>https://www.indeed.com/viewjob?jk=e963a76a96f6ee7d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Databricks, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e31b9336087ca67</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce9b3675d762e69</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI DevOps Engineering Intern</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nabors Industries</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f92799868c5370</t>
+          <t>https://www.indeed.com/viewjob?jk=470e1c7daa979f8e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Frontend Engineer, Growth</t>
+          <t>RDF Modeling AI Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Dassault Systèmes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d16cacc55a79a65</t>
+          <t>https://www.indeed.com/viewjob?jk=1946f8a80acb35ab</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Frontend Engineer, Growth</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>GAP Solutions, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+          <t>RAG, Synapse, AKS, Apache Airflow, Git, Databricks, Polars, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e03ea52757f6c20a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea56e4fa623ef1db</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Frontend Engineer, Growth</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130823613412f45e</t>
+          <t>https://www.indeed.com/viewjob?jk=052ff42df262f3f2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Frontend Engineer, Growth</t>
+          <t>Data Engineer, Integrations and Implementation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>KIZEN Technologies, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49aad56d323b86fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9645dfcd9784cb33</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Frontend Engineer, Growth</t>
+          <t>AI Business Solutions Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Hillwood Development Company, LLC.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Databricks, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b692d4b4514efb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=dc33af8f9cdb3faf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Frontend Engineer, Growth</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+          <t>Data Scientist, LangChain, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadf94f6c3802590</t>
+          <t>https://www.indeed.com/viewjob?jk=3f7ff3bb1144765a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Frontend Engineer, Growth</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d820b6fb355e099</t>
+          <t>https://www.indeed.com/viewjob?jk=aed26c292da5721f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Frontend Engineer, Growth</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>The Mosaic Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
+          <t>Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,427 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=260d2c211e08604c</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer, Growth</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6c3c6ab5aadbf7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer, Growth</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb44cf89ffe8d69</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer, Growth</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2eed596f2550187</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer, Growth</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba069fa2aa10643</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer, Growth</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c410cf2e6ed6cf30</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer, Growth</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9dae6cea31770b11</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer, Growth</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a690d8865abae1e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer, Growth</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62ec4d7e57257fa8</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer, Growth</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb5fcb7e9a3cd5fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer, Growth</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37cbf38f16601053</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Frontend Engineer, Growth</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Terraform, Kafka, MySQL, SQL, R, Java, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f2c978f71265748</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Entry Level Software Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>S3, Git, PostgreSQL, MongoDB, Dask, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3a3a650f5c651d</t>
+          <t>https://www.indeed.com/viewjob?jk=852dea3797f50b6c</t>
         </is>
       </c>
     </row>
